--- a/01_경혈별_해부생리_분석보고서/SP_족태음비경/SP06_삼음교/SP06_삼음교_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/SP_족태음비경/SP06_삼음교/SP06_삼음교_해부생리_분석데이터.xlsx
@@ -16,7 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주치분리" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기추론_TriTarget" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -492,7 +493,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡2</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -519,7 +520,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>T1/T2</t>
+          <t>Target 1≡2/Target 3</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -546,7 +547,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -573,7 +574,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>Target 3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -600,7 +601,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>T1/T2</t>
+          <t>Target 1≡2/Target 3</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -627,7 +628,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>Target 3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -654,7 +655,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>Target 3</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -681,7 +682,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -708,7 +709,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>Target 3</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -735,7 +736,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>T1/T2</t>
+          <t>Target 1≡2/Target 3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -762,12 +763,255 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>Target 3</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>배오·금기 기원</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>证治通鉴 明堂 주치·小结(한글번역)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>발바닥에 열이 남, 정강이가 아파 오래 서 있지 못함, 습비로 걷지 못함 / 『명당경』 삼음교는 8촌, 육조 이후 방서 삼음교는 대부분 3촌</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>중국침구증치통감(中国针灸证治通鉴)/中国针灸证治通鉴_05_第壹编_第七篇_足太阴脾经_手少阴心经_手太阳小肠经_한글번역.md L205, L249 (원문 L154, L184)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Target 1≡2 / Target 3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>기술(한글 번역본 기준, 불일치 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>证治通鉴 徐文伯·小结(한글번역)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>서문백이 침을 놓아 태아를 떨어뜨렸다… / 어떤 수혈서는 이 두 혈을 임부 금자혈로 꼽기까지 하였다</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>중국침구증치통감(中国针灸证治通鉴)/中国针灸证治通鉴_22_第叁编_妇儿科病证_한글번역.md L587, L743 (원문 L382, L480)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Target 3</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>기술(한글 번역본 기준, 불일치 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>证治通鉴 梦泄精(千金)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>梦泄精，灸三阴交二七壮…（内踝上大脉并四指是）/ 안쪽 복사뼈 위로 네 손가락… 큰 맥이 있는 곳</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>중국침구증치통감(中国针灸证治通鉴)/中国针灸证治通鉴_20_第叁编_内科病症_三十九霍乱至四十二遗精.md L1261 ; …_한글번역.md L2007</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Target 3</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3寸 촉진 표현 大脉 = 큰두렁정맥(추론)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>证治通鉴 痔漏 二阴交 按</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>一名二阴交 / 按：二阴交当是三阴交之误。六朝以前，三阴交与足太阴穴是两个不同的穴</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>중국침구증치통감(中国针灸证治通鉴)/中国针灸证治通鉴_26_第叁编_外科病证_痔漏至虫兽咬伤.md L20, L22 ; …_한글번역.md L28, L34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Target 3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Rank 4 필사 오류 교정</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 太阴·厥阴 8寸 교차</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>上踝八寸，交出太阴之后 / 循胫骨后交出厥阴之前 / 太阴从内踝上行八寸，当胫骨后，交出厥阴之前(杨上善) / 上踝八寸，而厥阴复出太阴之后(铜人)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_29_第叁编_第十二篇_足厥阴经脉、经别、络脉和经筋.md L65, L101 ; 중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_21_第叁编_第四篇_足太阴经脉、经别、络脉和经筋.md L162, L182</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Target 1≡2</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>경맥 순행 근거(혈명 직접 언급 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 송 이전 경맥도</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>医心方 足厥阴图: 三阴交 中郄 뒤 → 内踝上八寸 / 产经 十脉图: 三阴交 归 足厥阴 / 医心方 足太阴图: 太阴=今三阴交, 漏谷 뒤 阴交(三阴)=杨注明堂 三阴交, 值得深入研究</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_29_第叁编_第十二篇_足厥阴经脉、经别、络脉和经筋.md L313 ; 중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_02_第壹编_第二篇_经络学说的演变(一~七).md L1429 ; 중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_21_第叁编_第四篇_足太阴经脉、经别、络脉和经筋.md L362</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Target 1≡2</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>通考 ④·⑤ 증거 독립 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 足太阴穴 변천</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>除足太阴穴六朝以后变化较大外 / 玉匮针经 内踝后白肉际陷骨宛中 / 隋唐 多定于内踝上三寸 / 千金翼 逆产 针足太阴 内踝后白肉际(六朝以前定穴法) / 足太阴经内踝上三寸名三阴交</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_01_第壹编_第一篇_“经脉”概念的形成与经络学说的建立.md L586~587, L719, L731, L1067, L1199, L1225~1229</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Target 3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Target 3 계보 전사; 徐文伯 足太阴 자리 단정 유보</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 千金翼 二阴交</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>针足太阴，穴在内踝上一夫，一名二阴交</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_01_第壹编_第一篇_“经脉”概念的形成与经络学说的建立.md L1263</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Target 3</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>필사 오류(证治通鉴 按으로 三阴交 교정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 경락론 해석 비판</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>杨上善以为诸阴交即三阴交，似缺乏文献依据 / 没有凭据，或出于意会 / 过足太阴之三阴交(经络汇编·针灸逢源) / 甲乙 足太阴、厥阴、少阴之会</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_35_第肆编_第六篇_阴维脉与阳维脉.md L224 ; 중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_04_第壹编_第二篇_经络学说的演变(十二~十三).md L1014 ; 중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_29_第叁编_第十二篇_足厥阴经脉、经别、络脉和经筋.md L163, L198 ; 중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_25_第叁编_第八篇_足少阴经脉、经别、络脉和经筋.md L281 ; 중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_11_第贰编_第三篇_脉度、骨度与要穴.md L1084</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Target 3</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Rank 4 경락론적 과잉 확장 판별</t>
         </is>
       </c>
     </row>
@@ -782,7 +1026,293 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>X (내외측)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Y (상하)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Z / Δ(추정)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>근거·판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Target 1 (고전 문헌)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>明堂 在内踝上八寸胻骨下陷者中</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>정강뼈 안쪽모서리 뒤</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>안쪽복사 위 8寸</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>3푼 6.9mm</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>通考 L1125</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Target 2 (촉진 실체화·자입 기준점)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>胻骨下陷者中 = 정강뼈(FMA:24476) 안쪽모서리 뒤–가자미근(FMA:22542) 안쪽 가장자리 간극(緣)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>정강뼈 안쪽모서리 바로 뒤</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>8寸(최초 기술 높이)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>바닥 긴발가락굽힘근 FMA:51071(추론)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>8寸 높이 교재·실측 없음 → SP7 구성으로 추론</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Target 3 (WHO)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>内踝尖上3寸，胫骨内侧缘后际</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>정강뼈 안쪽모서리 바로 뒤</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>안쪽복사 끝 위 3寸</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>직자 1~1.5寸 23~34.5mm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>通考 L1107</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Δ T1–T2</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>약 0~5mm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>병합(같은 문장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Δ T1–T3</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>약 12~15cm</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>분기(Y 5寸 × 1寸≈2.5~3cm, 골도 13寸 추정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Δ T2–T3</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>약 12~15cm</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Target 1≡2 vs Target 3</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>분기 기준 Δ &gt; 10mm</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>ΔARI-Core 33.8, ± 비중첩 → Target 3 단독 우위; 10mm 기준으로 상태 바뀐 쌍 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>3寸 촉진 표현</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>甲乙(明刊)·千金翼 骨下陷者中, 千金 内踝上大脉并四指</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>정강뼈 안쪽모서리 뒤 / 큰두렁정맥(추론)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3寸</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Target 3과 10mm 이내 → 새 Target 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>구판 대응</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>구 T1(明堂 8寸) → Target 1≡2; 구 T2(현행 3寸) → Target 3</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>이중 채점 승계(위치 불변)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -832,6 +1362,28 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>정본 Rank 0~7</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 Framework 2.7.7(1·ARI·B-Check·주치·분기 시트)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>3대 원전 스크리닝, T1/T2 표기, 분기추론 시트 없음</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 5행·证治通鉴(한글번역 포함) 4행 추가(파일·행 포인터), T1→Target 1≡2·T2→Target 3 표기, ④ 通考·经络通鉴 교감 재점검(점수 불변), Tri-Target 좌표·Δ 시트 신설(Δ &gt; 10mm 기준)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Framework 2.7.7; 분기 기준 Δ &gt; 10mm(2026-10-25)</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1583,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>T1 심도(名实考)</t>
+          <t>Target 1≡2 심도(名实考)</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1857,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>Target 3</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1324,19 +1876,19 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>①50 ②100/75 ③75 ④100/75</t>
+          <t>①50 ②100/75 ③75 ④100/75 (④ 通考·经络通鉴 교감 2.7.7 재점검: 불변)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>通考 L1097~1385</t>
+          <t>通考 L1097~1385; 经络通鉴 1편 L719~1263</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>Target 3</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1367,7 +1919,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>Target 3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1398,7 +1950,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>Target 3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1431,7 +1983,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>Target 3</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1464,7 +2016,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡2</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1485,19 +2037,19 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>①100/75 ②25 ③75 ④75(조정)</t>
+          <t>①100/75 ②25 ③75 ④75(조정) (④ 通考·经络通鉴 교감 2.7.7 재점검: 值得深入研究·甲乙 3寸 이문 → 75 유지)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>通考 L1119~1173</t>
+          <t>通考 L1119~1173; 经络通鉴 21편 L182·L362, 29편 L65·L313, 2편 L1429</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1518,7 +2070,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>T1 교재·실측 없음, 추론만</t>
+          <t>Target 1≡2 교재·실측 없음, 추론만</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1530,7 +2082,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡2</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1561,7 +2113,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡2</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1592,7 +2144,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡2</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1642,7 +2194,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>± 구간 비중첩 → T2 우위</t>
+          <t>± 구간 비중첩 → Target 3 단독 우위 (Tri-Target 판정 규칙, 독립 Target 2개)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1896,7 +2448,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>합계(T2)</t>
+          <t>합계(Target 3)</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1921,7 +2473,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡2</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
@@ -3148,7 +3700,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Target 1≡2</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3170,7 +3722,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>Target 3</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -3192,7 +3744,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>Target 3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3214,7 +3766,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>Target 3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3236,7 +3788,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>Target 3</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
